--- a/Filtered_V3.0/COCWS_HCA__Florida__Westside__Hospital.xlsx
+++ b/Filtered_V3.0/COCWS_HCA__Florida__Westside__Hospital.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Abstracting </t>
+          <t>3M (360 Encompass)-ABSDPI</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Admissions </t>
+          <t>3M (360 Encompass)-ADMO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Charges </t>
+          <t>3M (360 Encompass)-ITSDIRO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS DI Results </t>
+          <t>3M (360 Encompass)-ITSHMRO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS HM Results </t>
+          <t>3M (360 Encompass)-ITSHMRO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS HM Results </t>
+          <t>3M (360 Encompass)-LABRES</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Lab Results (Discrete) </t>
+          <t>3M (360 Encompass)-OMORDO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-OM Orders </t>
+          <t>3M (360 Encompass)-Patient Accounting</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1237,22 +1237,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople ED Patient Visit Data</t>
+          <t>3M (360 Encompass)-iPeople EDM</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople Medication Administration</t>
+          <t>3M (360 Encompass)-iPeople Meds</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople Nursing Assessment Forms</t>
+          <t>3M (360 Encompass)-iPeople PCS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">AQuity Solutions (DocEP)-Admissions </t>
+          <t>AQuity Solutions (DocEP)-ADMO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">AQuity Solutions (DocEP)-ITS HM Results </t>
+          <t>AQuity Solutions (DocEP)-ITSHMRO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Airstrip Technologies (ONE)-Admissions </t>
+          <t>Airstrip Technologies (ONE)-ADMO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alere (MAS RALS-Plus)-</t>
+          <t>Alere (MAS RALS-Plus)-ADMO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1997,7 +1997,22 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -2019,7 +2034,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alere (MAS RALS-Plus)-Admissions </t>
+          <t>Alere (MAS RALS-Plus)-labpoc</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2064,22 +2079,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>ADMO</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>Inbound</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Admissions </t>
+          <t>BD (Pyxis Medstation ES)-ADMO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Pharmacy Inventory </t>
+          <t>BD (Pyxis Medstation ES)-PHAINV</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Pharmacy Orders </t>
+          <t>BD (Pyxis Medstation ES)-PHAORD</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computrition (Computrition)-Admissions </t>
+          <t>Computrition (Computrition)-ADMO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computrition (Computrition)-OM Orders </t>
+          <t>Computrition (Computrition)-OMORDO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Datavant/CIOX (HealthSource to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Datavant/CIOX (HealthSource to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dolbey (Fusion Voice)-Admissions </t>
+          <t>Dolbey (Fusion Voice)-ADMO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dolbey (Fusion)-</t>
+          <t>Dolbey (Fusion)-ITSDIRO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3015,7 +3015,22 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>ITSDIRO</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>ORU</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -3037,7 +3052,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dolbey (Fusion)-ITS DI Results </t>
+          <t>Dolbey (Fusion)-radord</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3082,22 +3097,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>ITSDIRO</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>Outbound</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-Admissions </t>
+          <t>Envision Healthcare (Envision Healthcare)-ADMO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-ITS HM Results </t>
+          <t>Envision Healthcare (Envision Healthcare)-CWSO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3313,17 +3313,17 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-ITS HM Results </t>
+          <t>Envision Healthcare (Envision Healthcare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-Scheduling </t>
+          <t>Envision Healthcare (Envision Healthcare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3472,22 +3472,22 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Envision Healthcare (Envision Healthcare)-iPeople ED Patient Visit Data</t>
+          <t>Envision Healthcare (Envision Healthcare)-iPeople EDM</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Florida HIE (Event Notification Service)-Admissions </t>
+          <t>Florida HIE (Event Notification Service)-ADMO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CMI - Carescape Gateway)-Admissions </t>
+          <t>GE (CMI - Carescape Gateway)-ADMO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CMI - Carescape Gateway)-Scheduling </t>
+          <t>GE (CMI - Carescape Gateway)-CWSO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>GE (Centricity - CCG PACS)-</t>
+          <t>GE (Centricity - CCG PACS)-ADMO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4069,6 +4069,21 @@
       <c r="P48" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -4090,7 +4105,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-Admissions </t>
+          <t>GE (Centricity - CCG PACS)-ITSDIRO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4140,17 +4155,17 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -4172,7 +4187,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-ITS DI Results </t>
+          <t>GE (Centricity - CCG PACS)-ITSDIUI</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4217,22 +4232,22 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSDIUI</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Radiology Image Status </t>
         </is>
       </c>
     </row>
@@ -4254,7 +4269,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-Radiology Image Status </t>
+          <t>GE (Centricity - CCG PACS)-ITSDIUI</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4336,7 +4351,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-Radiology Image Status </t>
+          <t>GE (Centricity - CCG PACS)-radord</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4381,22 +4396,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>ITSDIUI</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>ORM</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Radiology Image Status </t>
+          <t>Outbound</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW to Centricity Cardio Workflow-CCW)-ITS HM Results </t>
+          <t>GE (Centricity Cardio Workflow-CCW to Centricity Cardio Workflow-CCW)-ITSHMRO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>GE (Centricity Cardio Workflow-CCW to MPF-Patient Folder/HPF Facility)-</t>
+          <t>GE (Centricity Cardio Workflow-CCW to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-Admissions </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-ADMO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-Charges </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-ITSHMRO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4885,17 +4885,17 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-ITS HM Results </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-OMORDO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4962,22 +4962,22 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-OM Orders </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-Patient Accounting</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5044,22 +5044,22 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE to MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>GE (Centricity MUSE to MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-Admissions </t>
+          <t>GE (Centricity MUSE)-ADMO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-Charges </t>
+          <t>GE (Centricity MUSE)-ITSHMRO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5419,17 +5419,17 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-ITS HM Results </t>
+          <t>GE (Centricity MUSE)-OMORDO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5496,22 +5496,22 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -5533,7 +5533,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-OM Orders </t>
+          <t>GE (Centricity MUSE)-Patient Accounting</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5578,22 +5578,22 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -5677,7 +5677,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>GE (Centricity MacLab-DMS/CVPACS to MPF-Patient Folder/HPF Facility)-</t>
+          <t>GE (Centricity MacLab-DMS/CVPACS to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Edison Datalogue to MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>GE (Edison Datalogue to MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-</t>
+          <t>Google (Healthcare Data Engine - HDE)-ADMO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5996,6 +5996,21 @@
       <c r="P74" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -6017,7 +6032,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Admissions </t>
+          <t>Google (Healthcare Data Engine - HDE)-IMMUN</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6067,17 +6082,17 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6114,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-ITS DI Results </t>
+          <t>Google (Healthcare Data Engine - HDE)-ITSDIRO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6181,7 +6196,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-ITS HM Results </t>
+          <t>Google (Healthcare Data Engine - HDE)-ITSHMRO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6263,7 +6278,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Lab Results (Discrete) </t>
+          <t>Google (Healthcare Data Engine - HDE)-LABRES</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6345,7 +6360,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-MU-Immunizations</t>
+          <t>Google (Healthcare Data Engine - HDE)-LABRES2</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6395,17 +6410,17 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6442,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-Pathology Results</t>
+          <t>Google (Healthcare Data Engine - HDE)-PHAORD</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6477,17 +6492,17 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -6509,7 +6524,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Pharmacy Orders </t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople EDM</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6559,17 +6574,17 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6606,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople ED Patient Visit Data</t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople Meds</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6641,17 +6656,17 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6688,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople Medication Administration</t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople PCS</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6723,17 +6738,17 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -6755,7 +6770,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople Nursing Assessment Forms</t>
+          <t>Google (Healthcare Data Engine - HDE)-radord</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6801,21 +6816,6 @@
       <c r="P84" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-</t>
+          <t>HCA (Cloudera Kafka)-ADMO</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6945,6 +6945,21 @@
       <c r="P86" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -6966,7 +6981,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-</t>
+          <t>HCA (Cloudera Kafka)-CWSO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7012,6 +7027,21 @@
       <c r="P87" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>CWSO</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>SIU</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -7033,7 +7063,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Admissions </t>
+          <t>HCA (Cloudera Kafka)-IMMUN</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7083,17 +7113,17 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7145,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS DI Results </t>
+          <t>HCA (Cloudera Kafka)-ITSDIRO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7197,7 +7227,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS DI Results </t>
+          <t>HCA (Cloudera Kafka)-ITSDIRO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -7279,7 +7309,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS HM Results </t>
+          <t>HCA (Cloudera Kafka)-ITSHMRO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7361,7 +7391,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Lab Results (Discrete) </t>
+          <t>HCA (Cloudera Kafka)-LABRES</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7443,7 +7473,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Lab Results (Discrete) </t>
+          <t>HCA (Cloudera Kafka)-LABRES</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7525,7 +7555,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-MU-Immunizations</t>
+          <t>HCA (Cloudera Kafka)-LABRES2</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7575,17 +7605,17 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -7607,7 +7637,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-OM Orders </t>
+          <t>HCA (Cloudera Kafka)-LABRES2</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7657,17 +7687,17 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -7689,7 +7719,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-Pathology Results</t>
+          <t>HCA (Cloudera Kafka)-OMORDO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7739,17 +7769,17 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7801,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-Pathology Results</t>
+          <t>HCA (Cloudera Kafka)-PHAORD</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7821,17 +7851,17 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -7853,7 +7883,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Pharmacy Orders </t>
+          <t>HCA (Cloudera Kafka)-iPeople EDM</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7903,17 +7933,17 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7965,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Scheduling </t>
+          <t>HCA (Cloudera Kafka)-iPeople EDM</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7985,17 +8015,17 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -8017,7 +8047,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople ED Patient Visit Data</t>
+          <t>HCA (Cloudera Kafka)-iPeople Meds</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -8067,17 +8097,17 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -8099,7 +8129,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople ED Patient Visit Data</t>
+          <t>HCA (Cloudera Kafka)-iPeople PCS</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -8149,17 +8179,17 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8211,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Medication Administration</t>
+          <t>HCA (Cloudera Kafka)-iPeople PCS</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -8231,17 +8261,17 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8293,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Nursing Assessment Forms</t>
+          <t>HCA (Cloudera Kafka)-radord</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8309,21 +8339,6 @@
       <c r="P103" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R103" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8345,7 +8360,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Nursing Assessment Forms</t>
+          <t>HCA (Cloudera Kafka)-radord</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -8391,21 +8406,6 @@
       <c r="P104" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R104" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Revive)-ITS HM Results </t>
+          <t>HCA (Revive)-ITSHMRO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>HCA (SMART to Optiflex)-</t>
+          <t>HCA (SMART to Optiflex)-multi</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>HCA (SMART)-</t>
+          <t>HCA (SMART)-ADMO</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8807,7 +8807,22 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -8829,7 +8844,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>HCA (SMART)-</t>
+          <t>HCA (SMART)-multi</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8896,7 +8911,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (SMART)-Admissions </t>
+          <t>HCA (SMART)-multi</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8941,22 +8956,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q112" t="inlineStr">
-        <is>
-          <t>ADMO</t>
-        </is>
-      </c>
-      <c r="R112" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>Inbound</t>
         </is>
       </c>
     </row>
@@ -9040,7 +9040,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Care Management-Facility)-Admissions </t>
+          <t>HCA D&amp;IS (Care Management-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ADMO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -9230,6 +9230,21 @@
       <c r="P116" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -9251,7 +9266,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Admissions </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-CWSO</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -9301,17 +9316,17 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -9333,7 +9348,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-ITS DI Results </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-IMMUN</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -9383,17 +9398,17 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9430,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-ITS HM Results </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ITSDIRO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9465,7 +9480,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -9475,7 +9490,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -9497,7 +9512,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Lab Results (Discrete) </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ITSHMRO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -9547,7 +9562,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -9557,7 +9572,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -9579,7 +9594,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Electronic Lab Reporting</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-LABRES</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -9629,7 +9644,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>PHELR</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -9639,7 +9654,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>MU-Electronic Lab Reporting</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -9661,7 +9676,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Immunizations</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-LABRES2</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -9711,17 +9726,17 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -9743,7 +9758,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Syndromic Surveillance</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-OMORDO</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9793,17 +9808,17 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>PHSS</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>MU-Syndromic Surveillance</t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -9825,7 +9840,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-OM Orders </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHAORD</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9875,17 +9890,17 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -9907,7 +9922,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-Pathology Results</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHELR</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9957,7 +9972,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHELR</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -9967,7 +9982,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t>MU-Electronic Lab Reporting</t>
         </is>
       </c>
     </row>
@@ -9989,7 +10004,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Pharmacy Orders </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHSS</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -10039,17 +10054,17 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>PHSS</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>MU-Syndromic Surveillance</t>
         </is>
       </c>
     </row>
@@ -10071,7 +10086,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Scheduling </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-radord</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -10117,21 +10132,6 @@
       <c r="P127" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q127" t="inlineStr">
-        <is>
-          <t>CWSO</t>
-        </is>
-      </c>
-      <c r="R127" t="inlineStr">
-        <is>
-          <t>SIU</t>
-        </is>
-      </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -10215,7 +10215,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (FHIR Web Services)-Admissions </t>
+          <t>HCA D&amp;IS (FHIR Web Services)-ADMO</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -10297,7 +10297,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (FHIR Web Services)-Admissions </t>
+          <t>HCA D&amp;IS (FHIR Web Services)-ADMO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (MPF-Patient Folder/HPF Facility)-</t>
+          <t>HCA D&amp;IS (MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-</t>
+          <t>HCA D&amp;IS (Waterpark)-ADMO</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -10616,6 +10616,21 @@
       <c r="P134" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -10637,7 +10652,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Admissions </t>
+          <t>HCA D&amp;IS (Waterpark)-CWSO</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -10687,17 +10702,17 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -10719,7 +10734,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-ITS DI Results </t>
+          <t>HCA D&amp;IS (Waterpark)-IMMUN</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -10769,17 +10784,17 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -10801,7 +10816,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-ITS HM Results </t>
+          <t>HCA D&amp;IS (Waterpark)-IMMUNQRY</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -10851,7 +10866,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>IMMUNQRY</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -10861,7 +10876,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t>Immunization Query</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10898,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-Immunization Query</t>
+          <t>HCA D&amp;IS (Waterpark)-ITSDIRO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -10933,7 +10948,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>IMMUNQRY</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -10943,7 +10958,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>Immunization Query</t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -10965,7 +10980,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Lab Results (Discrete) </t>
+          <t>HCA D&amp;IS (Waterpark)-ITSHMRO</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -11015,7 +11030,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -11025,7 +11040,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -11047,7 +11062,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-MU-Immunizations</t>
+          <t>HCA D&amp;IS (Waterpark)-LABRES</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -11097,17 +11112,17 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -11129,7 +11144,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-MU-Syndromic Surveillance</t>
+          <t>HCA D&amp;IS (Waterpark)-LABRES2</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -11179,17 +11194,17 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>PHSS</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>MU-Syndromic Surveillance</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -11211,7 +11226,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-OM Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-OMORDO</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -11293,7 +11308,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-OM Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-OMORDO</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -11375,7 +11390,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-Pathology Results</t>
+          <t>HCA D&amp;IS (Waterpark)-PHAORD</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -11425,17 +11440,17 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -11457,7 +11472,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Pharmacy Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-PHSS</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -11507,17 +11522,17 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>PHSS</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>MU-Syndromic Surveillance</t>
         </is>
       </c>
     </row>
@@ -11539,7 +11554,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Scheduling </t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople EDM</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -11589,17 +11604,17 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -11621,7 +11636,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople ED Patient Visit Data</t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople Meds</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -11671,17 +11686,17 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -11703,7 +11718,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople Medication Administration</t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople PCS</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -11753,17 +11768,17 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -11785,7 +11800,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople Nursing Assessment Forms</t>
+          <t>HCA D&amp;IS (Waterpark)-radord</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -11831,21 +11846,6 @@
       <c r="P149" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q149" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R149" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -11929,7 +11929,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA Parallon (Charge Master)-SMART Procedure Codes </t>
+          <t>HCA Parallon (Charge Master)-MISPROC</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA Parallon (eCapture)-Admissions </t>
+          <t>HCA Parallon (eCapture)-ADMO</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -12217,7 +12217,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-Admissions </t>
+          <t>Health Catalyst (HCare Hub)-ADMO</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-ITS DI Results </t>
+          <t>Health Catalyst (HCare Hub)-ITSDIRO</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-ITS HM Results </t>
+          <t>Health Catalyst (HCare Hub)-ITSHMRO</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -12463,7 +12463,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-Lab Results (Discrete) </t>
+          <t>Health Catalyst (HCare Hub)-LABRES</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Health Catalyst (HCare Hub)-Pathology Results</t>
+          <t>Health Catalyst (HCare Hub)-LABRES2</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -12689,7 +12689,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hill-Rom (Navacare Patient Flow)-Admissions </t>
+          <t>Hill-Rom (Navacare Patient Flow)-ADMO</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -12833,7 +12833,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hill-Rom/Welch Allyn (Connex CS)-Admissions </t>
+          <t>Hill-Rom/Welch Allyn (Connex CS)-ADMO</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hill-Rom/Welch Allyn (Connex CS)-Clinical Monitoring Results </t>
+          <t>Hill-Rom/Welch Allyn (Connex CS)-PCSCMI</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -13059,7 +13059,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Admissions </t>
+          <t>Hospira (Theradoc)-ADMO</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -13141,7 +13141,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-ITS DI Results </t>
+          <t>Hospira (Theradoc)-ITSDIRO</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-ITS HM Results </t>
+          <t>Hospira (Theradoc)-ITSHMRO</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Lab Results (Discrete) </t>
+          <t>Hospira (Theradoc)-LABRES</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-OM Orders </t>
+          <t>Hospira (Theradoc)-OMORDO</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -13469,7 +13469,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Pharmacy Orders </t>
+          <t>Hospira (Theradoc)-PHAORD</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople ED Patient Visit Data</t>
+          <t>Hospira (Theradoc)-iPeople EDM</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -13633,7 +13633,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople Medication Administration</t>
+          <t>Hospira (Theradoc)-iPeople Meds</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople Nursing Assessment Forms</t>
+          <t>Hospira (Theradoc)-iPeople PCS</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -13859,7 +13859,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyland (Onbase RX-ADT/Link Orders)-Admissions </t>
+          <t>Hyland (Onbase RX-ADT/Link Orders)-ADMO</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Hyland (Onbase to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Hyland (Onbase to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -14132,7 +14132,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyland (Onbase)-Admissions </t>
+          <t>Hyland (Onbase)-ADMO</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -14276,7 +14276,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">IBM (Consent Management)-Admissions </t>
+          <t>IBM (Consent Management)-ADMO</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -14420,7 +14420,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">IM Practice Manager (Ingenious Med)-Admissions </t>
+          <t>IM Practice Manager (Ingenious Med)-ADMO</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -14564,7 +14564,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMS Integrated Medical Systems (ReadyTracker-Tissue)-Admissions </t>
+          <t>IMS Integrated Medical Systems (ReadyTracker-Tissue)-ADMO</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMS Integrated Medical Systems (ReadyTracker-Tissue)-Tissue Tracking </t>
+          <t>IMS Integrated Medical Systems (ReadyTracker-Tissue)-SURTSD</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -14790,7 +14790,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiate (Initiate)-Admissions </t>
+          <t>Initiate (Initiate)-ADMO</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -14872,7 +14872,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiate (Initiate)-Admissions </t>
+          <t>Initiate (Initiate)-ADMO</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -15016,7 +15016,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-</t>
+          <t>Iodine Software (Iodine-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -15062,6 +15062,21 @@
       <c r="P192" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -15083,7 +15098,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Admissions </t>
+          <t>Iodine Software (Iodine-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -15133,17 +15148,17 @@
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -15165,7 +15180,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-ITS DI Results </t>
+          <t>Iodine Software (Iodine-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -15215,7 +15230,7 @@
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R194" t="inlineStr">
@@ -15225,7 +15240,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -15247,7 +15262,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-ITS HM Results </t>
+          <t>Iodine Software (Iodine-Facility)-LABRES</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -15297,7 +15312,7 @@
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
@@ -15307,7 +15322,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -15329,7 +15344,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Lab Results (Discrete) </t>
+          <t>Iodine Software (Iodine-Facility)-LABRES2</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -15379,7 +15394,7 @@
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
@@ -15389,7 +15404,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -15411,7 +15426,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-OM Orders </t>
+          <t>Iodine Software (Iodine-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -15493,7 +15508,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-Pathology Results</t>
+          <t>Iodine Software (Iodine-Facility)-PHAORD</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -15543,17 +15558,17 @@
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -15575,7 +15590,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Pharmacy Orders </t>
+          <t>Iodine Software (Iodine-Facility)-iPeople EDM</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -15625,17 +15640,17 @@
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -15657,7 +15672,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-iPeople ED Patient Visit Data</t>
+          <t>Iodine Software (Iodine-Facility)-iPeople Meds</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -15707,17 +15722,17 @@
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -15739,7 +15754,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-iPeople Medication Administration</t>
+          <t>Iodine Software (Iodine-Facility)-iPeople PCS</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -15789,17 +15804,17 @@
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -15821,7 +15836,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-iPeople Nursing Assessment Forms</t>
+          <t>Iodine Software (Iodine-Facility)-radord</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -15867,21 +15882,6 @@
       <c r="P202" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q202" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R202" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -15965,7 +15965,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">MSN Healthcare Solutions (Intellirad)-Admissions </t>
+          <t>MSN Healthcare Solutions (Intellirad)-ADMO</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -16047,7 +16047,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">MSN Healthcare Solutions (Intellirad)-ITS DI Results </t>
+          <t>MSN Healthcare Solutions (Intellirad)-ITSDIRO</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -16191,7 +16191,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">McKesson (MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>McKesson (MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -16335,7 +16335,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medaxion (Medaxion Pulse to MPF-Patient Folder/HPF Facility)-Scanned Documents </t>
+          <t>Medaxion (Medaxion Pulse to MPF-Patient Folder/HPF Facility)-SCAIMG</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -16479,7 +16479,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medaxion (Medaxion Pulse)-Admissions </t>
+          <t>Medaxion (Medaxion Pulse)-ADMO</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -16561,7 +16561,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medaxion (Medaxion Pulse)-Scheduling </t>
+          <t>Medaxion (Medaxion Pulse)-CWSO</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -16705,7 +16705,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">MediMobile (MediMobile)-Admissions </t>
+          <t>MediMobile (MediMobile)-ADMO</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Meditech (HCA 5.6)-</t>
+          <t>Meditech (HCA 5.6)-ADMO</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -16895,6 +16895,21 @@
       <c r="P216" t="inlineStr">
         <is>
           <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -16916,7 +16931,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-Admissions </t>
+          <t>Meditech (HCA 5.6)-ITSDIRO</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -16966,17 +16981,17 @@
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -16998,7 +17013,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-ITS DI Results </t>
+          <t>Meditech (HCA 5.6)-ITSHMRO</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -17048,7 +17063,7 @@
       </c>
       <c r="Q218" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R218" t="inlineStr">
@@ -17058,7 +17073,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -17080,7 +17095,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-ITS HM Results </t>
+          <t>Meditech (HCA 5.6)-LABRES</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -17130,7 +17145,7 @@
       </c>
       <c r="Q219" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R219" t="inlineStr">
@@ -17140,7 +17155,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -17162,7 +17177,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-Lab Results (Discrete) </t>
+          <t>Meditech (HCA 5.6)-LABRES2</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -17212,7 +17227,7 @@
       </c>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
@@ -17222,7 +17237,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -17244,7 +17259,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-OM Orders </t>
+          <t>Meditech (HCA 5.6)-OMORDO</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -17326,7 +17341,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Meditech (HCA 5.6)-Pathology Results</t>
+          <t>Meditech (HCA 5.6)-PHAORD</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -17376,17 +17391,17 @@
       </c>
       <c r="Q222" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -17408,7 +17423,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-Pharmacy Orders </t>
+          <t>Meditech (HCA 5.6)-radord</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -17454,21 +17469,6 @@
       <c r="P223" t="inlineStr">
         <is>
           <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q223" t="inlineStr">
-        <is>
-          <t>PHAORD</t>
-        </is>
-      </c>
-      <c r="R223" t="inlineStr">
-        <is>
-          <t>RDE</t>
-        </is>
-      </c>
-      <c r="S223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -17552,7 +17552,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-Admissions </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ADMO</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -17634,7 +17634,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-ITS DI Results </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -17716,7 +17716,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-ITS DI Results </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -17798,7 +17798,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -17880,7 +17880,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-Scanned Documents </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-SCAIMG</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -18024,7 +18024,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mednax (BabySteps Cloud)-Admissions </t>
+          <t>Mednax (BabySteps Cloud)-ADMO</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -18168,7 +18168,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-Admissions </t>
+          <t>Midas+ (Care Management-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -18250,7 +18250,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-Admissions </t>
+          <t>Midas+ (Care Management-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -18332,7 +18332,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS DI Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -18414,7 +18414,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS HM Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -18496,7 +18496,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS HM Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -18640,7 +18640,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobile Heartbeat (imobile)-Admissions </t>
+          <t>Mobile Heartbeat (imobile)-ADMO</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobile Heartbeat (imobile)-Lab Results (Discrete) </t>
+          <t>Mobile Heartbeat (imobile)-LABRES</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Omnicell (Optiflex to SMART)-</t>
+          <t>Omnicell (Optiflex to SMART)-mmrepl</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -18995,7 +18995,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omnicell (Optiflex)-Admissions </t>
+          <t>Omnicell (Optiflex)-ADMO</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -19077,7 +19077,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omnicell (Optiflex)-Charges </t>
+          <t>Omnicell (Optiflex)-Patient Accounting</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Passport Health Communications, Inc. (eCare Next)-Admissions </t>
+          <t>Passport Health Communications, Inc. (eCare Next)-ADMO</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -19365,7 +19365,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Patient Keeper (Portal)-</t>
+          <t>Patient Keeper (Portal)-ITSHMRO</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -19411,6 +19411,21 @@
       <c r="P249" t="inlineStr">
         <is>
           <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>ITSHMRO</t>
+        </is>
+      </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>ORU</t>
+        </is>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -19432,7 +19447,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient Keeper (Portal)-ITS HM Results </t>
+          <t>Patient Keeper (Portal)-eps</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -19478,21 +19493,6 @@
       <c r="P250" t="inlineStr">
         <is>
           <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q250" t="inlineStr">
-        <is>
-          <t>ITSHMRO</t>
-        </is>
-      </c>
-      <c r="R250" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Team Health (Team Health)-Admissions </t>
+          <t>Team Health (Team Health)-ADMO</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -19720,7 +19720,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleSpecialists (TeleCare)-Admissions </t>
+          <t>TeleSpecialists (TeleCare)-ADMO</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -19802,7 +19802,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleSpecialists (TeleCare)-ITS HM Results </t>
+          <t>TeleSpecialists (TeleCare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -19884,7 +19884,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleSpecialists (TeleCare)-OM Orders </t>
+          <t>TeleSpecialists (TeleCare)-OMORDO</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -20028,7 +20028,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleTracking (TransferCenter IQ)-Admissions </t>
+          <t>TeleTracking (TransferCenter IQ)-ADMO</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -20110,7 +20110,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleTracking (TransferCenter IQ)-OM Orders </t>
+          <t>TeleTracking (TransferCenter IQ)-OMORDO</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -20192,7 +20192,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>TeleTracking (TransferCenter IQ)-iPeople Nursing Assessment Forms</t>
+          <t>TeleTracking (TransferCenter IQ)-iPeople PCS</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -20336,7 +20336,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telexy Healthcare Inc (Q-path)-Admissions </t>
+          <t>Telexy Healthcare Inc (Q-path)-ADMO</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -20480,7 +20480,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Ventana Medical Systems (VANTAGE)-</t>
+          <t>Ventana Medical Systems (VANTAGE)-pthord</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -20609,7 +20609,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Admissions </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -20691,7 +20691,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ITS DI Results </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -20773,7 +20773,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Lab Results (Discrete) </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-LABRES</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -20855,7 +20855,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OM Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -20937,7 +20937,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OM Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -21019,7 +21019,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Pharmacy Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-PHAORD</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -21101,7 +21101,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople ED Patient Visit Data</t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople EDM</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -21183,7 +21183,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople Medication Administration</t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople Meds</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -21327,7 +21327,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Volpara Health (Aspen Breast)-</t>
+          <t>Volpara Health (Aspen Breast)-radord</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -21456,7 +21456,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-</t>
+          <t>dbMotion (db Motion)-ADMO</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -21502,6 +21502,21 @@
       <c r="P277" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R277" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -21523,7 +21538,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Admissions </t>
+          <t>dbMotion (db Motion)-IMMUN</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -21573,17 +21588,17 @@
       </c>
       <c r="Q278" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -21605,7 +21620,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-ITS DI Results </t>
+          <t>dbMotion (db Motion)-ITSDIRO</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -21687,7 +21702,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-ITS HM Results </t>
+          <t>dbMotion (db Motion)-ITSHMRO</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -21769,7 +21784,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Lab Results (Discrete) </t>
+          <t>dbMotion (db Motion)-LABRES</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -21851,7 +21866,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-MU-Immunizations</t>
+          <t>dbMotion (db Motion)-LABRES2</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -21901,17 +21916,17 @@
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -21933,7 +21948,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-Pathology Results</t>
+          <t>dbMotion (db Motion)-PHAORD</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -21983,17 +21998,17 @@
       </c>
       <c r="Q283" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -22015,7 +22030,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Pharmacy Orders </t>
+          <t>dbMotion (db Motion)-iPeople EDM</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -22065,17 +22080,17 @@
       </c>
       <c r="Q284" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -22097,7 +22112,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-iPeople ED Patient Visit Data</t>
+          <t>dbMotion (db Motion)-iPeople PCS</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -22147,17 +22162,17 @@
       </c>
       <c r="Q285" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -22179,7 +22194,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-iPeople Nursing Assessment Forms</t>
+          <t>dbMotion (db Motion)-radord</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -22225,21 +22240,6 @@
       <c r="P286" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q286" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R286" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S286" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -22323,7 +22323,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>iPeople (HCA 5.6)-iPeople ED Patient Visit Data</t>
+          <t>iPeople (HCA 5.6)-iPeople EDM</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -22405,7 +22405,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>iPeople (HCA 5.6)-iPeople Medication Administration</t>
+          <t>iPeople (HCA 5.6)-iPeople Meds</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -22549,7 +22549,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t xml:space="preserve">iPeople (iPeople MT56)-OM Orders </t>
+          <t>iPeople (iPeople MT56)-OMORDO</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -22631,7 +22631,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>iPeople (iPeople MT56)-iPeople ED Patient Visit Data</t>
+          <t>iPeople (iPeople MT56)-iPeople EDM</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -22713,7 +22713,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>iPeople (iPeople MT56)-iPeople Medication Administration</t>
+          <t>iPeople (iPeople MT56)-iPeople Meds</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -22795,7 +22795,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>iPeople (iPeople MT56)-iPeople Nursing Assessment Forms</t>
+          <t>iPeople (iPeople MT56)-iPeople PCS</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
